--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N56_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N56_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.68574040306952</v>
+        <v>6.611432815498796</v>
       </c>
       <c r="D2" t="n">
-        <v>41.46245917762442</v>
+        <v>6.737649616363968</v>
       </c>
       <c r="E2" t="n">
-        <v>8.540883188156661</v>
+        <v>1.387893518075457</v>
       </c>
       <c r="F2" t="n">
-        <v>9.580354127650704</v>
+        <v>1.55680754574324</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>47.84763607343317</v>
+        <v>7.775240861932891</v>
       </c>
       <c r="D3" t="n">
-        <v>45.86194503761939</v>
+        <v>7.452566068613152</v>
       </c>
       <c r="E3" t="n">
-        <v>8.540883188156661</v>
+        <v>1.387893518075457</v>
       </c>
       <c r="F3" t="n">
-        <v>9.580354127650704</v>
+        <v>1.55680754574324</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>25.3731471742909</v>
+        <v>4.123136415822271</v>
       </c>
       <c r="D4" t="n">
-        <v>21.38367035905415</v>
+        <v>3.4748464333463</v>
       </c>
       <c r="E4" t="n">
-        <v>8.540883188156661</v>
+        <v>1.387893518075457</v>
       </c>
       <c r="F4" t="n">
-        <v>9.580354127650704</v>
+        <v>1.55680754574324</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>24.89827842846939</v>
+        <v>4.045970244626275</v>
       </c>
       <c r="D5" t="n">
-        <v>21.55020552163462</v>
+        <v>3.501908397265626</v>
       </c>
       <c r="E5" t="n">
-        <v>8.540883188156661</v>
+        <v>1.387893518075457</v>
       </c>
       <c r="F5" t="n">
-        <v>9.580354127650704</v>
+        <v>1.55680754574324</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>15.78261360819501</v>
+        <v>2.564674711331689</v>
       </c>
       <c r="D6" t="n">
-        <v>16.82460360644194</v>
+        <v>2.733998086046816</v>
       </c>
       <c r="E6" t="n">
-        <v>8.540883188156661</v>
+        <v>1.387893518075457</v>
       </c>
       <c r="F6" t="n">
-        <v>9.580354127650704</v>
+        <v>1.55680754574324</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>20.23768029965766</v>
+        <v>3.28862304869437</v>
       </c>
       <c r="D7" t="n">
-        <v>10.53460878126717</v>
+        <v>1.711873926955915</v>
       </c>
       <c r="E7" t="n">
-        <v>8.540883188156661</v>
+        <v>1.387893518075457</v>
       </c>
       <c r="F7" t="n">
-        <v>9.580354127650704</v>
+        <v>1.55680754574324</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>34.68506952869466</v>
+        <v>5.636323798412882</v>
       </c>
       <c r="D8" t="n">
-        <v>33.05617386871551</v>
+        <v>5.371628253666271</v>
       </c>
       <c r="E8" t="n">
-        <v>8.540883188156661</v>
+        <v>1.387893518075457</v>
       </c>
       <c r="F8" t="n">
-        <v>9.580354127650704</v>
+        <v>1.55680754574324</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>16.73512157976688</v>
+        <v>2.719457256712118</v>
       </c>
       <c r="D9" t="n">
-        <v>14.73876640816168</v>
+        <v>2.395049541326272</v>
       </c>
       <c r="E9" t="n">
-        <v>8.540883188156661</v>
+        <v>1.387893518075457</v>
       </c>
       <c r="F9" t="n">
-        <v>9.580354127650704</v>
+        <v>1.55680754574324</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>24.00312712902609</v>
+        <v>3.90050815846674</v>
       </c>
       <c r="D10" t="n">
-        <v>22.76959183115569</v>
+        <v>3.700058672562799</v>
       </c>
       <c r="E10" t="n">
-        <v>8.540883188156661</v>
+        <v>1.387893518075457</v>
       </c>
       <c r="F10" t="n">
-        <v>9.580354127650704</v>
+        <v>1.55680754574324</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>18.02463134744217</v>
+        <v>2.929002593959352</v>
       </c>
       <c r="D11" t="n">
-        <v>18.08931973341396</v>
+        <v>2.939514456679769</v>
       </c>
       <c r="E11" t="n">
-        <v>8.540883188156661</v>
+        <v>1.387893518075457</v>
       </c>
       <c r="F11" t="n">
-        <v>9.580354127650704</v>
+        <v>1.55680754574324</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>27.41751206120488</v>
+        <v>4.455345709945793</v>
       </c>
       <c r="D12" t="n">
-        <v>30.43725319003838</v>
+        <v>4.946053643381237</v>
       </c>
       <c r="E12" t="n">
-        <v>8.540883188156661</v>
+        <v>1.387893518075457</v>
       </c>
       <c r="F12" t="n">
-        <v>9.580354127650704</v>
+        <v>1.55680754574324</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>24.92245111895804</v>
+        <v>4.049898306830682</v>
       </c>
       <c r="D13" t="n">
-        <v>23.16720484269836</v>
+        <v>3.764670786938483</v>
       </c>
       <c r="E13" t="n">
-        <v>8.540883188156661</v>
+        <v>1.387893518075457</v>
       </c>
       <c r="F13" t="n">
-        <v>9.580354127650704</v>
+        <v>1.55680754574324</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>21.91881478520092</v>
+        <v>3.56180740259515</v>
       </c>
       <c r="D14" t="n">
-        <v>36.91814331443766</v>
+        <v>5.999198288596121</v>
       </c>
       <c r="E14" t="n">
-        <v>8.540883188156661</v>
+        <v>1.387893518075457</v>
       </c>
       <c r="F14" t="n">
-        <v>9.580354127650704</v>
+        <v>1.55680754574324</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>31.82941255500632</v>
+        <v>5.172279540188528</v>
       </c>
       <c r="D15" t="n">
-        <v>27.87166735296775</v>
+        <v>4.529145944857261</v>
       </c>
       <c r="E15" t="n">
-        <v>8.540883188156661</v>
+        <v>1.387893518075457</v>
       </c>
       <c r="F15" t="n">
-        <v>9.580354127650704</v>
+        <v>1.55680754574324</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>34.30549018894579</v>
+        <v>5.574642155703691</v>
       </c>
       <c r="D16" t="n">
-        <v>35.00426656844933</v>
+        <v>5.688193317373017</v>
       </c>
       <c r="E16" t="n">
-        <v>8.540883188156661</v>
+        <v>1.387893518075457</v>
       </c>
       <c r="F16" t="n">
-        <v>9.580354127650704</v>
+        <v>1.55680754574324</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>30.71556348572011</v>
+        <v>4.991279066429518</v>
       </c>
       <c r="D17" t="n">
-        <v>32.66996496313136</v>
+        <v>5.308869306508846</v>
       </c>
       <c r="E17" t="n">
-        <v>8.540883188156661</v>
+        <v>1.387893518075457</v>
       </c>
       <c r="F17" t="n">
-        <v>9.580354127650704</v>
+        <v>1.55680754574324</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>39.55290555378229</v>
+        <v>6.427347152489622</v>
       </c>
       <c r="D18" t="n">
-        <v>39.63542096748389</v>
+        <v>6.440755907216132</v>
       </c>
       <c r="E18" t="n">
-        <v>8.540883188156661</v>
+        <v>1.387893518075457</v>
       </c>
       <c r="F18" t="n">
-        <v>9.580354127650704</v>
+        <v>1.55680754574324</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>37.1705113375741</v>
+        <v>6.040208092355791</v>
       </c>
       <c r="D19" t="n">
-        <v>37.36173122377579</v>
+        <v>6.071281323863566</v>
       </c>
       <c r="E19" t="n">
-        <v>8.540883188156661</v>
+        <v>1.387893518075457</v>
       </c>
       <c r="F19" t="n">
-        <v>9.580354127650704</v>
+        <v>1.55680754574324</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>28.60040109007929</v>
+        <v>4.647565177137886</v>
       </c>
       <c r="D20" t="n">
-        <v>28.66382684244031</v>
+        <v>4.65787186189655</v>
       </c>
       <c r="E20" t="n">
-        <v>8.540883188156661</v>
+        <v>1.387893518075457</v>
       </c>
       <c r="F20" t="n">
-        <v>9.580354127650704</v>
+        <v>1.55680754574324</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
